--- a/it_forms/029_network_security_quiz--it_forms.xlsx
+++ b/it_forms/029_network_security_quiz--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'a_firewall_is_a_physical_barrier.'}</t>
+          <t>a_firewall_is_a_physical_barrier.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'A firewall is a physical barrier.'}</t>
+          <t>A firewall is a physical barrier.</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'a_firewall_is_a_software_barrier.'}</t>
+          <t>a_firewall_is_a_software_barrier.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'A firewall is a software barrier.'}</t>
+          <t>A firewall is a software barrier.</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'a_firewall_is_a_network-based_security_system.'}</t>
+          <t>a_firewall_is_a_network-based_security_system.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'A firewall is a network-based security system.'}</t>
+          <t>A firewall is a network-based security system.</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'a_firewall_is_a_hardware-based_security_system.'}</t>
+          <t>a_firewall_is_a_hardware-based_security_system.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'A firewall is a hardware-based security system.'}</t>
+          <t>A firewall is a hardware-based security system.</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'a_firewall_is_installed_to_identify_and_prevent_unauthorized_access.'}</t>
+          <t>a_firewall_is_installed_to_identify_and_prevent_unauthorized_access.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'A firewall is installed to identify and prevent unauthorized access.'}</t>
+          <t>A firewall is installed to identify and prevent unauthorized access.</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'a_router_is_installed_to_identify_and_prevent_unauthorized_access.'}</t>
+          <t>a_router_is_installed_to_identify_and_prevent_unauthorized_access.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'A router is installed to identify and prevent unauthorized access.'}</t>
+          <t>A router is installed to identify and prevent unauthorized access.</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'a_network_switch_is_installed_to_identify_and_prevent_unauthorized_access.'}</t>
+          <t>a_network_switch_is_installed_to_identify_and_prevent_unauthorized_access.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'A network switch is installed to identify and prevent unauthorized access.'}</t>
+          <t>A network switch is installed to identify and prevent unauthorized access.</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'an_intrusion_detection_system_is_installed_to_identify_and_prevent_unauthorized_access.'}</t>
+          <t>an_intrusion_detection_system_is_installed_to_identify_and_prevent_unauthorized_access.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'An intrusion detection system is installed to identify and prevent unauthorized access.'}</t>
+          <t>An intrusion detection system is installed to identify and prevent unauthorized access.</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'firewall'}</t>
+          <t>firewall</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Firewall'}</t>
+          <t>Firewall</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'network_switch'}</t>
+          <t>network_switch</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Network switch'}</t>
+          <t>Network switch</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'router'}</t>
+          <t>router</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Router'}</t>
+          <t>Router</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'intrusion_detection_system'}</t>
+          <t>intrusion_detection_system</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Intrusion detection system'}</t>
+          <t>Intrusion detection system</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'identifying_and_alerting_the_network_administrator.'}</t>
+          <t>identifying_and_alerting_the_network_administrator.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Identifying and alerting the network administrator.'}</t>
+          <t>Identifying and alerting the network administrator.</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'identifying_and_preventing_unauthorized_access.'}</t>
+          <t>identifying_and_preventing_unauthorized_access.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Identifying and preventing unauthorized access.'}</t>
+          <t>Identifying and preventing unauthorized access.</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'identifying,_alerting,_and_preventing_unauthorized_access.'}</t>
+          <t>identifying,_alerting,_and_preventing_unauthorized_access.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Identifying, alerting, and preventing unauthorized access.'}</t>
+          <t>Identifying, alerting, and preventing unauthorized access.</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'identifying,_alerting,_and_blocking_malicious_traffic.'}</t>
+          <t>identifying,_alerting,_and_blocking_malicious_traffic.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Identifying, alerting, and blocking malicious traffic.'}</t>
+          <t>Identifying, alerting, and blocking malicious traffic.</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'phishing'}</t>
+          <t>phishing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Phishing'}</t>
+          <t>Phishing</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'sql_injection'}</t>
+          <t>sql_injection</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'SQL Injection'}</t>
+          <t>SQL Injection</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'cross-site_scripting'}</t>
+          <t>cross-site_scripting</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Cross-Site Scripting'}</t>
+          <t>Cross-Site Scripting</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'ransomware'}</t>
+          <t>ransomware</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Ransomware'}</t>
+          <t>Ransomware</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'a_network_switch_is_a_networked_device.'}</t>
+          <t>a_network_switch_is_a_networked_device.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'A network switch is a networked device.'}</t>
+          <t>A network switch is a networked device.</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'a_network_router_is_a_networked_device.'}</t>
+          <t>a_network_router_is_a_networked_device.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'A network router is a networked device.'}</t>
+          <t>A network router is a networked device.</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'a_network_switch_is_a_hardware-based_device.'}</t>
+          <t>a_network_switch_is_a_hardware-based_device.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'A network switch is a hardware-based device.'}</t>
+          <t>A network switch is a hardware-based device.</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'a_network_router_is_a_software-based_device.'}</t>
+          <t>a_network_router_is_a_software-based_device.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'A network router is a software-based device.'}</t>
+          <t>A network router is a software-based device.</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'to_reduce_network_latency.'}</t>
+          <t>to_reduce_network_latency.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'To reduce network latency.'}</t>
+          <t>To reduce network latency.</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'to_increase_network_bandwidth.'}</t>
+          <t>to_increase_network_bandwidth.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'To increase network bandwidth.'}</t>
+          <t>To increase network bandwidth.</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'to_reduce_network_complexity.'}</t>
+          <t>to_reduce_network_complexity.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'To reduce network complexity.'}</t>
+          <t>To reduce network complexity.</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'to_separate_sensitive_data.'}</t>
+          <t>to_separate_sensitive_data.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'To separate sensitive data.'}</t>
+          <t>To separate sensitive data.</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'to_prevent_network_threats.'}</t>
+          <t>to_prevent_network_threats.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'To prevent network threats.'}</t>
+          <t>To prevent network threats.</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'to_identify_and_respond_to_network_threats.'}</t>
+          <t>to_identify_and_respond_to_network_threats.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'To identify and respond to network threats.'}</t>
+          <t>To identify and respond to network threats.</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'to_educate_users_on_network_security.'}</t>
+          <t>to_educate_users_on_network_security.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'To educate users on network security.'}</t>
+          <t>To educate users on network security.</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'to_reduce_network_downtime.'}</t>
+          <t>to_reduce_network_downtime.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'To reduce network downtime.'}</t>
+          <t>To reduce network downtime.</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'a_network_security_policy_is_mandatory.'}</t>
+          <t>a_network_security_policy_is_mandatory.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'A network security policy is mandatory.'}</t>
+          <t>A network security policy is mandatory.</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'a_network_security_policy_is_advisory.'}</t>
+          <t>a_network_security_policy_is_advisory.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'A network security policy is advisory.'}</t>
+          <t>A network security policy is advisory.</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'a_network_security_policy_is_a_network_configuration.'}</t>
+          <t>a_network_security_policy_is_a_network_configuration.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'A network security policy is a network configuration.'}</t>
+          <t>A network security policy is a network configuration.</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'a_network_security_standard_is_a_network_configuration.'}</t>
+          <t>a_network_security_standard_is_a_network_configuration.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'A network security standard is a network configuration.'}</t>
+          <t>A network security standard is a network configuration.</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'network_security_is_not_necessary_for_all_systems.'}</t>
+          <t>network_security_is_not_necessary_for_all_systems.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Network security is not necessary for all systems.'}</t>
+          <t>Network security is not necessary for all systems.</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'network_security_is_necessary_but_not_sufficient.'}</t>
+          <t>network_security_is_necessary_but_not_sufficient.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Network security is necessary but not sufficient.'}</t>
+          <t>Network security is necessary but not sufficient.</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'network_security_is_necessary_and_sufficient.'}</t>
+          <t>network_security_is_necessary_and_sufficient.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Network security is necessary and sufficient.'}</t>
+          <t>Network security is necessary and sufficient.</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'network_security_is_not_a_priority.'}</t>
+          <t>network_security_is_not_a_priority.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Network security is not a priority.'}</t>
+          <t>Network security is not a priority.</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'to_ensure_network_security_compliance.'}</t>
+          <t>to_ensure_network_security_compliance.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'To ensure network security compliance.'}</t>
+          <t>To ensure network security compliance.</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'to_identify_network_vulnerabilities.'}</t>
+          <t>to_identify_network_vulnerabilities.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'To identify network vulnerabilities.'}</t>
+          <t>To identify network vulnerabilities.</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'to_prevent_network_threats.'}</t>
+          <t>to_prevent_network_threats.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'To prevent network threats.'}</t>
+          <t>To prevent network threats.</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'to_identify_and_prevent_network_threats.'}</t>
+          <t>to_identify_and_prevent_network_threats.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'To identify and prevent network threats.'}</t>
+          <t>To identify and prevent network threats.</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'to_respond_to_network_threats.'}</t>
+          <t>to_respond_to_network_threats.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'To respond to network threats.'}</t>
+          <t>To respond to network threats.</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'to_prevent_network_threats.'}</t>
+          <t>to_prevent_network_threats.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'To prevent network threats.'}</t>
+          <t>To prevent network threats.</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'to_identify_and_respond_to_network_threats.'}</t>
+          <t>to_identify_and_respond_to_network_threats.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'To identify and respond to network threats.'}</t>
+          <t>To identify and respond to network threats.</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'to_identify_and_prevent_network_threats.'}</t>
+          <t>to_identify_and_prevent_network_threats.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'To identify and prevent network threats.'}</t>
+          <t>To identify and prevent network threats.</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'network_segmentation_reduces_network_latency.'}</t>
+          <t>network_segmentation_reduces_network_latency.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'Network segmentation reduces network latency.'}</t>
+          <t>Network segmentation reduces network latency.</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'network_segmentation_reduces_network_bandwidth.'}</t>
+          <t>network_segmentation_reduces_network_bandwidth.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'Network segmentation reduces network bandwidth.'}</t>
+          <t>Network segmentation reduces network bandwidth.</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'network_segmentation_reduces_network_complexity.'}</t>
+          <t>network_segmentation_reduces_network_complexity.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'Network segmentation reduces network complexity.'}</t>
+          <t>Network segmentation reduces network complexity.</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'network_segmentation_separates_sensitive_data.'}</t>
+          <t>network_segmentation_separates_sensitive_data.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Network segmentation separates sensitive data.'}</t>
+          <t>Network segmentation separates sensitive data.</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'to_design_and_implement_network_devices.'}</t>
+          <t>to_design_and_implement_network_devices.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'To design and implement network devices.'}</t>
+          <t>To design and implement network devices.</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'to_configure_network_devices.'}</t>
+          <t>to_configure_network_devices.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'To configure network devices.'}</t>
+          <t>To configure network devices.</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'to_document_network_devices.'}</t>
+          <t>to_document_network_devices.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'To document network devices.'}</t>
+          <t>To document network devices.</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'to_design_and_document_network_architecture.'}</t>
+          <t>to_design_and_document_network_architecture.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'To design and document network architecture.'}</t>
+          <t>To design and document network architecture.</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_'network_segmentation_separates_sensitive_data.'}</t>
+          <t>network_segmentation_separates_sensitive_data.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': 'Network segmentation separates sensitive data.'}</t>
+          <t>Network segmentation separates sensitive data.</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'label':_'network_segmentation_reduces_network_latency.'}</t>
+          <t>network_segmentation_reduces_network_latency.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'label': 'Network segmentation reduces network latency.'}</t>
+          <t>Network segmentation reduces network latency.</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'label':_'network_segmentation_reduces_network_complexity.'}</t>
+          <t>network_segmentation_reduces_network_complexity.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'label': 'Network segmentation reduces network complexity.'}</t>
+          <t>Network segmentation reduces network complexity.</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'label':_'network_segmentation_reduces_network_downtime.'}</t>
+          <t>network_segmentation_reduces_network_downtime.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'label': 'Network segmentation reduces network downtime.'}</t>
+          <t>Network segmentation reduces network downtime.</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'label':_'to_design_and_implement_network_devices.'}</t>
+          <t>to_design_and_implement_network_devices.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'label': 'To design and implement network devices.'}</t>
+          <t>To design and implement network devices.</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'label':_'to_configure_network_devices.'}</t>
+          <t>to_configure_network_devices.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'label': 'To configure network devices.'}</t>
+          <t>To configure network devices.</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'label':_'to_educate_users_on_network_security.'}</t>
+          <t>to_educate_users_on_network_security.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'label': 'To educate users on network security.'}</t>
+          <t>To educate users on network security.</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'label':_'to_document_network_devices.'}</t>
+          <t>to_document_network_devices.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'label': 'To document network devices.'}</t>
+          <t>To document network devices.</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'label':_'network_access_control_is_mandatory.'}</t>
+          <t>network_access_control_is_mandatory.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'label': 'Network access control is mandatory.'}</t>
+          <t>Network access control is mandatory.</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'label':_'network_access_control_is_advisory.'}</t>
+          <t>network_access_control_is_advisory.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'label': 'Network access control is advisory.'}</t>
+          <t>Network access control is advisory.</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'label':_'network_access_control_is_a_network_configuration.'}</t>
+          <t>network_access_control_is_a_network_configuration.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'label': 'Network access control is a network configuration.'}</t>
+          <t>Network access control is a network configuration.</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'label':_'network_access_control_is_a_network_security_standard.'}</t>
+          <t>network_access_control_is_a_network_security_standard.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'label': 'Network access control is a network security standard.'}</t>
+          <t>Network access control is a network security standard.</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'label':_'to_manage_network_threats.'}</t>
+          <t>to_manage_network_threats.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'label': 'To manage network threats.'}</t>
+          <t>To manage network threats.</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'label':_'to_manage_network_assets.'}</t>
+          <t>to_manage_network_assets.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'label': 'To manage network assets.'}</t>
+          <t>To manage network assets.</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'label':_'to_manage_network_devices.'}</t>
+          <t>to_manage_network_devices.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'label': 'To manage network devices.'}</t>
+          <t>To manage network devices.</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'label':_'to_manage_network_services.'}</t>
+          <t>to_manage_network_services.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'label': 'To manage network services.'}</t>
+          <t>To manage network services.</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'label':_'network_security_awareness_training_is_not_necessary_for_all_employees.'}</t>
+          <t>network_security_awareness_training_is_not_necessary_for_all_employees.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'label': 'Network security awareness training is not necessary for all employees.'}</t>
+          <t>Network security awareness training is not necessary for all employees.</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'label':_'network_security_awareness_training_is_necessary_but_not_sufficient.'}</t>
+          <t>network_security_awareness_training_is_necessary_but_not_sufficient.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'label': 'Network security awareness training is necessary but not sufficient.'}</t>
+          <t>Network security awareness training is necessary but not sufficient.</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'label':_'network_security_awareness_training_is_necessary_and_sufficient.'}</t>
+          <t>network_security_awareness_training_is_necessary_and_sufficient.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'label': 'Network security awareness training is necessary and sufficient.'}</t>
+          <t>Network security awareness training is necessary and sufficient.</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'label':_'network_security_awareness_training_is_not_a_priority.'}</t>
+          <t>network_security_awareness_training_is_not_a_priority.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'label': 'Network security awareness training is not a priority.'}</t>
+          <t>Network security awareness training is not a priority.</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'label':_'to_educate_users_on_network_security.'}</t>
+          <t>to_educate_users_on_network_security.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'label': 'To educate users on network security.'}</t>
+          <t>To educate users on network security.</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'label':_'to_train_users_on_network_security.'}</t>
+          <t>to_train_users_on_network_security.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'label': 'To train users on network security.'}</t>
+          <t>To train users on network security.</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'label':_'to_design_and_implement_network_security_awareness_programs.'}</t>
+          <t>to_design_and_implement_network_security_awareness_programs.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'label': 'To design and implement network security awareness programs.'}</t>
+          <t>To design and implement network security awareness programs.</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'label':_'to_document_network_security_awareness_programs.'}</t>
+          <t>to_document_network_security_awareness_programs.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'label': 'To document network security awareness programs.'}</t>
+          <t>To document network security awareness programs.</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'label':_'to_respond_to_network_threats.'}</t>
+          <t>to_respond_to_network_threats.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'label': 'To respond to network threats.'}</t>
+          <t>To respond to network threats.</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'label':_'to_identify_network_threats.'}</t>
+          <t>to_identify_network_threats.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'label': 'To identify network threats.'}</t>
+          <t>To identify network threats.</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'label':_'to_prevent_network_threats.'}</t>
+          <t>to_prevent_network_threats.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'label': 'To prevent network threats.'}</t>
+          <t>To prevent network threats.</t>
         </is>
       </c>
     </row>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'label':_'to_identify_and_prevent_network_threats.'}</t>
+          <t>to_identify_and_prevent_network_threats.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'label': 'To identify and prevent network threats.'}</t>
+          <t>To identify and prevent network threats.</t>
         </is>
       </c>
     </row>
